--- a/SGC-CKN/Excel/baec2af9-9e1d-43a2-ace1-4a3a985ccaac_P7-14_P7-14_D800_22-03-2026.xlsx
+++ b/SGC-CKN/Excel/baec2af9-9e1d-43a2-ace1-4a3a985ccaac_P7-14_P7-14_D800_22-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="69">
   <si>
     <t>Dự án</t>
   </si>
@@ -154,6 +154,9 @@
   <si>
     <t xml:space="preserve">22:10
 21/03/2026</t>
+  </si>
+  <si>
+    <t>Thời gian bắt đầu được điều chỉnh từ 20:00 thành 20:10 để liên tục với lớp 5</t>
   </si>
   <si>
     <t>16</t>
@@ -1407,24 +1410,24 @@
         <v>4.62</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D17" s="27" t="s">
         <v>44</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F17" s="25">
         <v>-35</v>
@@ -1447,19 +1450,19 @@
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>47</v>
-      </c>
       <c r="E18" s="30" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F18" s="28">
         <v>-37.5</v>
@@ -1482,19 +1485,19 @@
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="32" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B19" s="32" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="34" t="s">
-        <v>50</v>
-      </c>
       <c r="E19" s="34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F19" s="32">
         <v>-39.5</v>
@@ -1512,24 +1515,24 @@
         <v>5.14</v>
       </c>
       <c r="K19" s="33" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B20" s="35" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="36" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D20" s="37" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E20" s="37" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F20" s="35">
         <v>-42.5</v>
@@ -1547,12 +1550,12 @@
         <v>4.2</v>
       </c>
       <c r="K20" s="36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="38" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B23" s="38"/>
       <c r="C23" s="38"/>
@@ -1658,31 +1661,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1867,7 +1870,7 @@
         <v>10</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1896,7 +1899,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1925,7 +1928,7 @@
         <v>10</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D10" s="32">
         <v>1</v>
@@ -1954,7 +1957,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D11" s="35">
         <v>1</v>
@@ -1977,7 +1980,7 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="39" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B12" s="40" t="s">
         <v>29</v>
